--- a/traobang.be/traobang.be/Templates/ImportKhoa.xlsx
+++ b/traobang.be/traobang.be/Templates/ImportKhoa.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>STT</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Tên khoa</t>
+  </si>
+  <si>
+    <t>Tên khoa trên mã QR</t>
   </si>
 </sst>
 </file>
@@ -382,15 +385,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.5703125" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -400,6 +404,9 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
